--- a/Listino_Italia.xlsx
+++ b/Listino_Italia.xlsx
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>2.337</v>
+        <v>2.332</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="H2" s="12" t="n">
-        <v>7311.1</v>
+        <v>7295.5</v>
       </c>
       <c r="I2" s="10" t="n">
         <v>0.22</v>
@@ -917,7 +917,7 @@
         <v/>
       </c>
       <c r="L2" s="14" t="n">
-        <v>1.4129382</v>
+        <v>1.4099153</v>
       </c>
       <c r="M2" s="15">
         <f>IF(OR(L2="",K2="",K2&lt;=0),"",L2/K2)</f>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>11.865</v>
+        <v>11.86</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="H4" s="12" t="n">
-        <v>3147.2</v>
+        <v>3145.8</v>
       </c>
       <c r="I4" s="10" t="n">
         <v>0.31</v>
@@ -1149,7 +1149,7 @@
         <v/>
       </c>
       <c r="L4" s="14" t="n">
-        <v>2.4243972</v>
+        <v>2.4233754</v>
       </c>
       <c r="M4" s="15">
         <f>IF(OR(L4="",K4="",K4&lt;=0),"",L4/K4)</f>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>37.54</v>
+        <v>37.57</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="H6" s="12" t="n">
-        <v>5323.9</v>
+        <v>5328.1</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>3.72</v>
@@ -1381,7 +1381,7 @@
         <v/>
       </c>
       <c r="L6" s="14" t="n">
-        <v>2.679706</v>
+        <v>2.6818473</v>
       </c>
       <c r="M6" s="15">
         <f>IF(OR(L6="",K6="",K6&lt;=0),"",L6/K6)</f>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>14.852</v>
+        <v>14.872</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="H8" s="12" t="n">
-        <v>30949</v>
+        <v>30990.7</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>1.05</v>
@@ -1615,7 +1615,7 @@
         <v/>
       </c>
       <c r="L8" s="14" t="n">
-        <v>1.7130334</v>
+        <v>1.7153403</v>
       </c>
       <c r="M8" s="15">
         <f>IF(OR(L8="",K8="",K8&lt;=0),"",L8/K8)</f>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>66.40000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="H9" s="12" t="n">
-        <v>7563.6</v>
+        <v>7569.3</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>4.61</v>
@@ -1730,7 +1730,7 @@
         <v/>
       </c>
       <c r="L9" s="14" t="n">
-        <v>4.7831726</v>
+        <v>4.786774</v>
       </c>
       <c r="M9" s="15">
         <f>IF(OR(L9="",K9="",K9&lt;=0),"",L9/K9)</f>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>14.98</v>
+        <v>14.97</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="H10" s="12" t="n">
-        <v>915</v>
+        <v>914.4</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>5.33</v>
@@ -1845,7 +1845,7 @@
         <v/>
       </c>
       <c r="L10" s="14" t="n">
-        <v>0.43163806</v>
+        <v>0.43134993</v>
       </c>
       <c r="M10" s="15">
         <f>IF(OR(L10="",K10="",K10&lt;=0),"",L10/K10)</f>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>23.72</v>
+        <v>23.74</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="H11" s="12" t="n">
-        <v>17536.6</v>
+        <v>17551.3</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>1.56</v>
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="L11" s="14" t="n">
-        <v>3.9013157</v>
+        <v>3.9046054</v>
       </c>
       <c r="M11" s="15">
         <f>IF(OR(L11="",K11="",K11&lt;=0),"",L11/K11)</f>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>11.72</v>
+        <v>11.724</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35610.3</v>
+        <v>35622.4</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>1.38</v>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1.2526721</v>
+        <v>1.2530996</v>
       </c>
       <c r="M12" s="15">
         <f>IF(OR(L12="",K12="",K12&lt;=0),"",L12/K12)</f>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>16.25</v>
+        <v>16.28</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="H14" s="12" t="n">
-        <v>24457.3</v>
+        <v>24502.5</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>1.38</v>
@@ -2305,7 +2305,7 @@
         <v/>
       </c>
       <c r="L14" s="14" t="n">
-        <v>1.5923567</v>
+        <v>1.5952965</v>
       </c>
       <c r="M14" s="15">
         <f>IF(OR(L14="",K14="",K14&lt;=0),"",L14/K14)</f>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>18.58</v>
+        <v>18.6</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2442.8</v>
+        <v>2445.4</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>1.02</v>
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="L15" s="14" t="n">
-        <v>1.6388816</v>
+        <v>1.6406457</v>
       </c>
       <c r="M15" s="15">
         <f>IF(OR(L15="",K15="",K15&lt;=0),"",L15/K15)</f>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>10.54</v>
+        <v>10.58</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="H16" s="12" t="n">
-        <v>3352.9</v>
+        <v>3365.6</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>0.68</v>
@@ -2533,7 +2533,7 @@
         <v/>
       </c>
       <c r="L16" s="14" t="n">
-        <v>1.4377302</v>
+        <v>1.4431865</v>
       </c>
       <c r="M16" s="15">
         <f>IF(OR(L16="",K16="",K16&lt;=0),"",L16/K16)</f>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>91.31999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6209.8</v>
+        <v>6211.1</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>1.99</v>
@@ -2650,7 +2650,7 @@
         <v/>
       </c>
       <c r="L17" s="14" t="n">
-        <v>11.332837</v>
+        <v>11.335319</v>
       </c>
       <c r="M17" s="15">
         <f>IF(OR(L17="",K17="",K17&lt;=0),"",L17/K17)</f>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>42.2</v>
+        <v>42.18</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>7448.8</v>
+        <v>7445.3</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>5.09</v>
@@ -2767,7 +2767,7 @@
         <v/>
       </c>
       <c r="L18" s="14" t="n">
-        <v>1.0779331</v>
+        <v>1.0774223</v>
       </c>
       <c r="M18" s="15">
         <f>IF(OR(L18="",K18="",K18&lt;=0),"",L18/K18)</f>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>19.9</v>
+        <v>19.89</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6758.9</v>
+        <v>6755.5</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>1.57</v>
@@ -3005,7 +3005,7 @@
         <v/>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.4494865</v>
+        <v>1.448758</v>
       </c>
       <c r="M20" s="15">
         <f>IF(OR(L20="",K20="",K20&lt;=0),"",L20/K20)</f>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4809.7</v>
+        <v>4824</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>3.19</v>
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="L21" s="14" t="n">
-        <v>1.685055</v>
+        <v>1.6900702</v>
       </c>
       <c r="M21" s="15">
         <f>IF(OR(L21="",K21="",K21&lt;=0),"",L21/K21)</f>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5.802</v>
+        <v>5.804</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="H22" s="12" t="n">
-        <v>6958.7</v>
+        <v>6961.1</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>0.23</v>
@@ -3239,7 +3239,7 @@
         <v/>
       </c>
       <c r="L22" s="14" t="n">
-        <v>1.7433894</v>
+        <v>1.7439903</v>
       </c>
       <c r="M22" s="15">
         <f>IF(OR(L22="",K22="",K22&lt;=0),"",L22/K22)</f>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>10.034</v>
+        <v>10.02</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>99570</v>
+        <v>99431.10000000001</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>0.38</v>
@@ -3588,7 +3588,7 @@
         <v/>
       </c>
       <c r="L25" s="14" t="n">
-        <v>3.007794</v>
+        <v>3.0035973</v>
       </c>
       <c r="M25" s="15">
         <f>IF(OR(L25="",K25="",K25&lt;=0),"",L25/K25)</f>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>24.135</v>
+        <v>24.08</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="H26" s="12" t="n">
-        <v>70039.8</v>
+        <v>69880.2</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>1.23</v>
@@ -3705,7 +3705,7 @@
         <v/>
       </c>
       <c r="L26" s="14" t="n">
-        <v>1.6624191</v>
+        <v>1.6586307</v>
       </c>
       <c r="M26" s="15">
         <f>IF(OR(L26="",K26="",K26&lt;=0),"",L26/K26)</f>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>345.35</v>
+        <v>345.65</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="H29" s="12" t="n">
-        <v>60704.5</v>
+        <v>60757.3</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>9.279999999999999</v>
@@ -4058,7 +4058,7 @@
         <v/>
       </c>
       <c r="L29" s="14" t="n">
-        <v>16.60656</v>
+        <v>16.620985</v>
       </c>
       <c r="M29" s="15">
         <f>IF(OR(L29="",K29="",K29&lt;=0),"",L29/K29)</f>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>13.77</v>
+        <v>13.825</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="H30" s="12" t="n">
-        <v>4919.8</v>
+        <v>4939.5</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>0.57</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="L30" s="14" t="n">
-        <v>4.478049</v>
+        <v>4.495935</v>
       </c>
       <c r="M30" s="15">
         <f>IF(OR(L30="",K30="",K30&lt;=0),"",L30/K30)</f>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>24.46</v>
+        <v>24.47</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>14965.1</v>
+        <v>14971.2</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>1.1</v>
@@ -4294,7 +4294,7 @@
         <v/>
       </c>
       <c r="L31" s="14" t="n">
-        <v>5.5351887</v>
+        <v>5.5374517</v>
       </c>
       <c r="M31" s="15">
         <f>IF(OR(L31="",K31="",K31&lt;=0),"",L31/K31)</f>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>9.141999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1684.2</v>
+        <v>1681.9</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>-6</v>
@@ -4409,7 +4409,7 @@
         <v/>
       </c>
       <c r="L32" s="14" t="n">
-        <v>0.88192165</v>
+        <v>0.880764</v>
       </c>
       <c r="M32" s="15">
         <f>IF(OR(L32="",K32="",K32&lt;=0),"",L32/K32)</f>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>3.91</v>
+        <v>3.908</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>5780.4</v>
+        <v>5777.5</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>0.32</v>
@@ -4643,7 +4643,7 @@
         <v/>
       </c>
       <c r="L34" s="14" t="n">
-        <v>1.406981</v>
+        <v>1.4062612</v>
       </c>
       <c r="M34" s="15">
         <f>IF(OR(L34="",K34="",K34&lt;=0),"",L34/K34)</f>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>6.475</v>
+        <v>6.47</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5846.1</v>
+        <v>5841.5</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>0.37</v>
@@ -4760,7 +4760,7 @@
         <v/>
       </c>
       <c r="L35" s="14" t="n">
-        <v>1.8708465</v>
+        <v>1.8694018</v>
       </c>
       <c r="M35" s="15">
         <f>IF(OR(L35="",K35="",K35&lt;=0),"",L35/K35)</f>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>35.62</v>
+        <v>35.58</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3743.5</v>
+        <v>3739.3</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>1.96</v>
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="L36" s="14" t="n">
-        <v>1.7585782</v>
+        <v>1.7566035</v>
       </c>
       <c r="M36" s="15">
         <f>IF(OR(L36="",K36="",K36&lt;=0),"",L36/K36)</f>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>6.75</v>
+        <v>6.751</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>118330.1</v>
+        <v>118347.7</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>0.5600000000000001</v>
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="L37" s="14" t="n">
-        <v>1.7002518</v>
+        <v>1.7005037</v>
       </c>
       <c r="M37" s="15">
         <f>IF(OR(L37="",K37="",K37&lt;=0),"",L37/K37)</f>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>9.087999999999999</v>
+        <v>9.086</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="H39" s="12" t="n">
-        <v>9238.200000000001</v>
+        <v>9236.1</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>0.7</v>
@@ -5226,7 +5226,7 @@
         <v/>
       </c>
       <c r="L39" s="14" t="n">
-        <v>2.4170213</v>
+        <v>2.4164896</v>
       </c>
       <c r="M39" s="15">
         <f>IF(OR(L39="",K39="",K39&lt;=0),"",L39/K39)</f>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>56.54</v>
+        <v>56.57</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="H42" s="12" t="n">
-        <v>32617.1</v>
+        <v>32634.4</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>1.95</v>
@@ -5571,7 +5571,7 @@
         <v/>
       </c>
       <c r="L42" s="14" t="n">
-        <v>3.3386478</v>
+        <v>3.3404193</v>
       </c>
       <c r="M42" s="15">
         <f>IF(OR(L42="",K42="",K42&lt;=0),"",L42/K42)</f>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>24.17</v>
+        <v>24.19</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>5641.7</v>
+        <v>5646.4</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>0.91</v>
@@ -5688,7 +5688,7 @@
         <v/>
       </c>
       <c r="L43" s="14" t="n">
-        <v>25.203337</v>
+        <v>25.224194</v>
       </c>
       <c r="M43" s="15">
         <f>IF(OR(L43="",K43="",K43&lt;=0),"",L43/K43)</f>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>2.662</v>
+        <v>2.652</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1862.4</v>
+        <v>1855.4</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>0.3</v>
@@ -5805,7 +5805,7 @@
         <v/>
       </c>
       <c r="L44" s="14" t="n">
-        <v>0.5346455</v>
+        <v>0.53263706</v>
       </c>
       <c r="M44" s="15">
         <f>IF(OR(L44="",K44="",K44&lt;=0),"",L44/K44)</f>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>12.94</v>
+        <v>12.96</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>4214.2</v>
+        <v>4220.7</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>0.83</v>
@@ -6043,7 +6043,7 @@
         <v/>
       </c>
       <c r="L46" s="14" t="n">
-        <v>5.9303393</v>
+        <v>5.939505</v>
       </c>
       <c r="M46" s="15">
         <f>IF(OR(L46="",K46="",K46&lt;=0),"",L46/K46)</f>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>28.13</v>
+        <v>28.15</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="H47" s="12" t="n">
-        <v>22687.8</v>
+        <v>22703.9</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>1.47</v>
@@ -6160,7 +6160,7 @@
         <v/>
       </c>
       <c r="L47" s="14" t="n">
-        <v>1.9843397</v>
+        <v>1.9857506</v>
       </c>
       <c r="M47" s="15">
         <f>IF(OR(L47="",K47="",K47&lt;=0),"",L47/K47)</f>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>49.92</v>
+        <v>49.97</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="H48" s="12" t="n">
-        <v>13577.7</v>
+        <v>13591.3</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>2.35</v>
@@ -6279,7 +6279,7 @@
         <v/>
       </c>
       <c r="L48" s="14" t="n">
-        <v>3.7212074</v>
+        <v>3.7249348</v>
       </c>
       <c r="M48" s="15">
         <f>IF(OR(L48="",K48="",K48&lt;=0),"",L48/K48)</f>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>2.14</v>
+        <v>2.135</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>554.6</v>
+        <v>553.3</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>0.2</v>
@@ -6396,7 +6396,7 @@
         <v/>
       </c>
       <c r="L49" s="14" t="n">
-        <v>1.7598686</v>
+        <v>1.7557566</v>
       </c>
       <c r="M49" s="15">
         <f>IF(OR(L49="",K49="",K49&lt;=0),"",L49/K49)</f>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>4.359</v>
+        <v>4.365</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="H50" s="12" t="n">
-        <v>5111</v>
+        <v>5118</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>-2.79</v>
@@ -6513,7 +6513,7 @@
         <v/>
       </c>
       <c r="L50" s="14" t="n">
-        <v>0.72384596</v>
+        <v>0.72484225</v>
       </c>
       <c r="M50" s="15">
         <f>IF(OR(L50="",K50="",K50&lt;=0),"",L50/K50)</f>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>6.555</v>
+        <v>6.535</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="H51" s="12" t="n">
-        <v>7111.4</v>
+        <v>7089.7</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>0.51</v>
@@ -6630,7 +6630,7 @@
         <v/>
       </c>
       <c r="L51" s="14" t="n">
-        <v>1.0807914</v>
+        <v>1.0774938</v>
       </c>
       <c r="M51" s="15">
         <f>IF(OR(L51="",K51="",K51&lt;=0),"",L51/K51)</f>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>27.05</v>
+        <v>27.03</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>34986.2</v>
+        <v>34960.3</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>1.85</v>
@@ -6747,7 +6747,7 @@
         <v/>
       </c>
       <c r="L52" s="14" t="n">
-        <v>2.5649536</v>
+        <v>2.5630572</v>
       </c>
       <c r="M52" s="15">
         <f>IF(OR(L52="",K52="",K52&lt;=0),"",L52/K52)</f>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>121.7</v>
+        <v>121.85</v>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="H53" s="12" t="n">
-        <v>35566.2</v>
+        <v>35610</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>4.81</v>
@@ -6864,7 +6864,7 @@
         <v/>
       </c>
       <c r="L53" s="14" t="n">
-        <v>5.0541964</v>
+        <v>5.0604258</v>
       </c>
       <c r="M53" s="15">
         <f>IF(OR(L53="",K53="",K53&lt;=0),"",L53/K53)</f>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="H54" s="12" t="n">
-        <v>484.3</v>
+        <v>482.2</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>0.11</v>
@@ -6981,7 +6981,7 @@
         <v/>
       </c>
       <c r="L54" s="14" t="n">
-        <v>1.0528684</v>
+        <v>1.0483689</v>
       </c>
       <c r="M54" s="15">
         <f>IF(OR(L54="",K54="",K54&lt;=0),"",L54/K54)</f>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>46.325</v>
+        <v>46.3</v>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="H57" s="12" t="n">
-        <v>41316.2</v>
+        <v>41293.9</v>
       </c>
       <c r="I57" s="10" t="n">
         <v>0.44</v>
@@ -7324,7 +7324,7 @@
         <v/>
       </c>
       <c r="L57" s="14" t="n">
-        <v>2.7003388</v>
+        <v>2.6988816</v>
       </c>
       <c r="M57" s="15">
         <f>IF(OR(L57="",K57="",K57&lt;=0),"",L57/K57)</f>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>4.348</v>
+        <v>4.349</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>8436.299999999999</v>
+        <v>8438.299999999999</v>
       </c>
       <c r="I58" s="10" t="n">
         <v>0.13</v>
@@ -7445,7 +7445,7 @@
         <v/>
       </c>
       <c r="L58" s="14" t="n">
-        <v>3.1994114</v>
+        <v>3.2001472</v>
       </c>
       <c r="M58" s="15">
         <f>IF(OR(L58="",K58="",K58&lt;=0),"",L58/K58)</f>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>9.475</v>
+        <v>9.525</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="H59" s="12" t="n">
-        <v>1569.8</v>
+        <v>1578.1</v>
       </c>
       <c r="I59" s="10" t="n">
         <v>-0.3</v>
@@ -7562,7 +7562,7 @@
         <v/>
       </c>
       <c r="L59" s="14" t="n">
-        <v>2.6548054</v>
+        <v>2.6688147</v>
       </c>
       <c r="M59" s="15">
         <f>IF(OR(L59="",K59="",K59&lt;=0),"",L59/K59)</f>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>4.874</v>
+        <v>4.889</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>18361.9</v>
+        <v>18418.4</v>
       </c>
       <c r="I61" s="10" t="n">
         <v>-6.77</v>
@@ -7794,7 +7794,7 @@
         <v/>
       </c>
       <c r="L61" s="14" t="n">
-        <v>0.25439742</v>
+        <v>0.25518033</v>
       </c>
       <c r="M61" s="15">
         <f>IF(OR(L61="",K61="",K61&lt;=0),"",L61/K61)</f>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>25.18</v>
+        <v>25.16</v>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="H63" s="12" t="n">
-        <v>25422.7</v>
+        <v>25402.5</v>
       </c>
       <c r="I63" s="10" t="n">
         <v>1.65</v>
@@ -8026,7 +8026,7 @@
         <v/>
       </c>
       <c r="L63" s="14" t="n">
-        <v>1.7155</v>
+        <v>1.7141374</v>
       </c>
       <c r="M63" s="15">
         <f>IF(OR(L63="",K63="",K63&lt;=0),"",L63/K63)</f>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>10.12</v>
+        <v>10.115</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>20308.4</v>
+        <v>20298.4</v>
       </c>
       <c r="I64" s="10" t="n">
         <v>0.5600000000000001</v>
@@ -8147,7 +8147,7 @@
         <v/>
       </c>
       <c r="L64" s="14" t="n">
-        <v>2.2803063</v>
+        <v>2.2791796</v>
       </c>
       <c r="M64" s="15">
         <f>IF(OR(L64="",K64="",K64&lt;=0),"",L64/K64)</f>
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>84.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="H65" s="12" t="n">
-        <v>127083.9</v>
+        <v>127128.8</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>7.05</v>
@@ -8264,7 +8264,7 @@
         <v/>
       </c>
       <c r="L65" s="14" t="n">
-        <v>1.8828804</v>
+        <v>1.8835464</v>
       </c>
       <c r="M65" s="15">
         <f>IF(OR(L65="",K65="",K65&lt;=0),"",L65/K65)</f>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>28.4</v>
+        <v>28.41</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="H66" s="12" t="n">
-        <v>20368.6</v>
+        <v>20375.8</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>2.03</v>
@@ -8379,7 +8379,7 @@
         <v/>
       </c>
       <c r="L66" s="14" t="n">
-        <v>2.0427246</v>
+        <v>2.043444</v>
       </c>
       <c r="M66" s="15">
         <f>IF(OR(L66="",K66="",K66&lt;=0),"",L66/K66)</f>
